--- a/artfynd/A 38965-2023 artfynd.xlsx
+++ b/artfynd/A 38965-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113680709</v>
+        <v>113680707</v>
       </c>
       <c r="B2" t="n">
-        <v>90146</v>
+        <v>90148</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>675273</v>
+        <v>675270</v>
       </c>
       <c r="R2" t="n">
-        <v>7079477</v>
+        <v>7079519</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680707</v>
+        <v>113680709</v>
       </c>
       <c r="B3" t="n">
-        <v>90146</v>
+        <v>90148</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675270</v>
+        <v>675273</v>
       </c>
       <c r="R3" t="n">
-        <v>7079519</v>
+        <v>7079477</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 38965-2023 artfynd.xlsx
+++ b/artfynd/A 38965-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113680707</v>
+        <v>113680709</v>
       </c>
       <c r="B2" t="n">
-        <v>90148</v>
+        <v>90149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>675270</v>
+        <v>675273</v>
       </c>
       <c r="R2" t="n">
-        <v>7079519</v>
+        <v>7079477</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680709</v>
+        <v>113680707</v>
       </c>
       <c r="B3" t="n">
-        <v>90148</v>
+        <v>90149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675273</v>
+        <v>675270</v>
       </c>
       <c r="R3" t="n">
-        <v>7079477</v>
+        <v>7079519</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 38965-2023 artfynd.xlsx
+++ b/artfynd/A 38965-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113680709</v>
+        <v>113680707</v>
       </c>
       <c r="B2" t="n">
-        <v>90149</v>
+        <v>90153</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>675273</v>
+        <v>675270</v>
       </c>
       <c r="R2" t="n">
-        <v>7079477</v>
+        <v>7079519</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680707</v>
+        <v>113680709</v>
       </c>
       <c r="B3" t="n">
-        <v>90149</v>
+        <v>90153</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675270</v>
+        <v>675273</v>
       </c>
       <c r="R3" t="n">
-        <v>7079519</v>
+        <v>7079477</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 38965-2023 artfynd.xlsx
+++ b/artfynd/A 38965-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113680707</v>
+        <v>113680709</v>
       </c>
       <c r="B2" t="n">
         <v>90153</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>675270</v>
+        <v>675273</v>
       </c>
       <c r="R2" t="n">
-        <v>7079519</v>
+        <v>7079477</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680709</v>
+        <v>113680707</v>
       </c>
       <c r="B3" t="n">
         <v>90153</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675273</v>
+        <v>675270</v>
       </c>
       <c r="R3" t="n">
-        <v>7079477</v>
+        <v>7079519</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 38965-2023 artfynd.xlsx
+++ b/artfynd/A 38965-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113680709</v>
+        <v>113680707</v>
       </c>
       <c r="B2" t="n">
         <v>90153</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>675273</v>
+        <v>675270</v>
       </c>
       <c r="R2" t="n">
-        <v>7079477</v>
+        <v>7079519</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680707</v>
+        <v>113680709</v>
       </c>
       <c r="B3" t="n">
         <v>90153</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675270</v>
+        <v>675273</v>
       </c>
       <c r="R3" t="n">
-        <v>7079519</v>
+        <v>7079477</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 38965-2023 artfynd.xlsx
+++ b/artfynd/A 38965-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
